--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487032_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487032_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3307</v>
+        <v>2.6847</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9608</v>
+        <v>2.2613</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3699</v>
+        <v>0.4234</v>
       </c>
       <c r="G2" t="n">
         <v>2.5475</v>
@@ -610,13 +610,13 @@
         <v>0.965</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2168</v>
+        <v>0.1372</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2829</v>
+        <v>0.0175</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. BARNES HERNANDEZ</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4331</v>
+        <v>1.2545</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1409</v>
+        <v>1.0797</v>
       </c>
       <c r="F3" t="n">
-        <v>1.574</v>
+        <v>0.1748</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1902</v>
+        <v>3.5371</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1655</v>
+        <v>-1.1519</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9752999999999999</v>
+        <v>4.689</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1183</v>
+        <v>4.378</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9312</v>
+        <v>0.4709</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1871</v>
+        <v>3.9071</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3085</v>
+        <v>-0.8409</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0968</v>
+        <v>-1.6227</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7883</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3161</v>
+        <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2373</v>
+        <v>-0.0896</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3291</v>
+        <v>-0.4032</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5664</v>
+        <v>0.3136</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>L. BARNES HERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2264</v>
+        <v>0.218</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5601</v>
+        <v>-1.2222</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3338</v>
+        <v>1.4402</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5371</v>
+        <v>-0.1902</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1519</v>
+        <v>-1.1655</v>
       </c>
       <c r="I4" t="n">
-        <v>4.689</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>4.378</v>
+        <v>1.1183</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4709</v>
+        <v>0.9312</v>
       </c>
       <c r="L4" t="n">
-        <v>3.9071</v>
+        <v>0.1871</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8409</v>
+        <v>-1.3085</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6227</v>
+        <v>-2.0968</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7883</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9301</v>
+        <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1177</v>
+        <v>0.0221</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9227</v>
+        <v>-0.4104</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.195</v>
+        <v>0.4326</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1824</v>
+        <v>-0.1299</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9882</v>
+        <v>-0.8285</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8058</v>
+        <v>0.6987</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3286</v>
@@ -844,13 +844,13 @@
         <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5909</v>
+        <v>-0.5384</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7139</v>
+        <v>-0.5542</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1229</v>
+        <v>0.0159</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>R. NUÑEZ HERRERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.467</v>
+        <v>-3.3742</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9379</v>
+        <v>-3.4953</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5291</v>
+        <v>0.121</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.5011</v>
+        <v>-0.4527</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3547</v>
+        <v>0.267</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1464</v>
+        <v>-0.7197</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.806</v>
+        <v>0.9089</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9524</v>
+        <v>1.6093</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1464</v>
+        <v>-0.7004</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6951</v>
+        <v>-1.3616</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4023</v>
+        <v>-1.3423</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2928</v>
+        <v>-0.0193</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5441</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R6" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9063</v>
+        <v>-0.9915</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1263</v>
+        <v>-0.8298</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7799</v>
+        <v>-0.1616</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3281</v>
+        <v>0.2859</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. NUÑEZ HERRERO</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.7609</v>
+        <v>-3.3821</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.8552</v>
+        <v>-2.6388</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.7433</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4527</v>
+        <v>-2.5011</v>
       </c>
       <c r="H7" t="n">
-        <v>0.267</v>
+        <v>-2.3547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7197</v>
+        <v>-0.1464</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9089</v>
+        <v>-0.806</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6093</v>
+        <v>-0.9524</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7004</v>
+        <v>0.1464</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3616</v>
+        <v>-1.6951</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3423</v>
+        <v>-1.4023</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0193</v>
+        <v>-0.2928</v>
       </c>
       <c r="P7" t="n">
+        <v>-1.5441</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-1.9301</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-3.8602</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3782</v>
+        <v>0.9911</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1898</v>
+        <v>0.4254</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1884</v>
+        <v>0.5658</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2859</v>
+        <v>-0.3281</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8321</v>
+        <v>-3.5257</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0042</v>
+        <v>-0.6443</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8279</v>
+        <v>-2.8814</v>
       </c>
       <c r="G8" t="n">
         <v>-3.3854</v>
@@ -1078,13 +1078,13 @@
         <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3953</v>
+        <v>0.7016</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3278</v>
+        <v>0.0321</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7231</v>
+        <v>0.6696</v>
       </c>
       <c r="V8" t="n">
         <v>-1.228</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>J. LAMBAS VIVANCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3991</v>
+        <v>-4.7695</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6535</v>
+        <v>-0.4135</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7456</v>
+        <v>-4.356</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.9244</v>
+        <v>-2.7805</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.1972</v>
+        <v>-1.7274</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7272</v>
+        <v>-1.0532</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.3232</v>
+        <v>0.6562</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6963</v>
+        <v>-0.6055</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6269</v>
+        <v>1.2617</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6012</v>
+        <v>-3.4367</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5009</v>
+        <v>-1.1219</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1003</v>
+        <v>-2.3149</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2275</v>
+        <v>-0.5909</v>
       </c>
       <c r="T9" t="n">
-        <v>1.051</v>
+        <v>-0.4134</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1765</v>
+        <v>-0.1775</v>
       </c>
       <c r="V9" t="n">
-        <v>1.228</v>
+        <v>-2.1701</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5138</v>
+        <v>-0.6562</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LAMBAS VIVANCOS</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2038</v>
+        <v>-5.5086</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7139</v>
+        <v>-4.7362</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4898</v>
+        <v>-0.7723</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7805</v>
+        <v>-4.9244</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7274</v>
+        <v>-3.1972</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0532</v>
+        <v>-1.7272</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6562</v>
+        <v>-3.3232</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6055</v>
+        <v>-2.6963</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2617</v>
+        <v>-0.6269</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.4367</v>
+        <v>-1.6012</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1219</v>
+        <v>-0.5009</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.3149</v>
+        <v>-1.1003</v>
       </c>
       <c r="P10" t="n">
-        <v>0.772</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R10" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0252</v>
+        <v>0.118</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7139</v>
+        <v>-0.0317</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3113</v>
+        <v>0.1497</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1701</v>
+        <v>1.228</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6562</v>
+        <v>1.5138</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5138</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.5173</v>
+        <v>-7.2981</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8963</v>
+        <v>-5.4362</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.621</v>
+        <v>-1.8619</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0115</v>
@@ -1312,13 +1312,13 @@
         <v>0.386</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0033</v>
+        <v>0.2224</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7588</v>
+        <v>-0.2987</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7621</v>
+        <v>0.5212</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8094</v>
+        <v>-7.7559</v>
       </c>
       <c r="E12" t="n">
         <v>-4.331</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4784</v>
+        <v>-3.4248</v>
       </c>
       <c r="G12" t="n">
         <v>-5.9033</v>
@@ -1390,13 +1390,13 @@
         <v>1.7371</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4852</v>
+        <v>-0.4316</v>
       </c>
       <c r="T12" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.037</v>
+        <v>0.0165</v>
       </c>
       <c r="V12" t="n">
         <v>-1.228</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-32.1818</v>
+        <v>-31.5868</v>
       </c>
       <c r="E13" t="n">
-        <v>-21.0002</v>
+        <v>-20.405</v>
       </c>
       <c r="F13" t="n">
         <v>-11.1816</v>
@@ -1447,16 +1447,16 @@
         <v>-4.5707</v>
       </c>
       <c r="L13" t="n">
-        <v>5.565999999999999</v>
+        <v>5.566000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-21.388</v>
+        <v>-21.38800000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-13.723</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.6651</v>
+        <v>-7.665099999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-5.790299999999999</v>
@@ -1468,13 +1468,13 @@
         <v>13.5105</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0443</v>
+        <v>-0.4496000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.5097</v>
+        <v>-2.9145</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4653</v>
+        <v>2.4654</v>
       </c>
       <c r="V13" t="n">
         <v>-4.9542</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. OSES TOME</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.615</v>
+        <v>9.1023</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5917</v>
+        <v>3.7227</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0234</v>
+        <v>5.3797</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1946</v>
+        <v>6.438</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7337</v>
+        <v>2.0297</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4609</v>
+        <v>4.4084</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7656</v>
+        <v>4.6556</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5589</v>
+        <v>0.7813</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2067</v>
+        <v>3.8743</v>
       </c>
       <c r="M14" t="n">
-        <v>1.429</v>
+        <v>1.7824</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1748</v>
+        <v>1.2483</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2542</v>
+        <v>0.5341</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3161</v>
+        <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1236</v>
+        <v>0.464</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4019</v>
+        <v>0.0321</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2783</v>
+        <v>0.4319</v>
       </c>
       <c r="V14" t="n">
-        <v>1.228</v>
+        <v>0.6562</v>
       </c>
       <c r="W14" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>P. OSES TOME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.4275</v>
+        <v>9.0959</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4222</v>
+        <v>4.9922</v>
       </c>
       <c r="F15" t="n">
-        <v>5.0052</v>
+        <v>4.1037</v>
       </c>
       <c r="G15" t="n">
-        <v>6.438</v>
+        <v>5.1946</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0297</v>
+        <v>1.7337</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4084</v>
+        <v>3.4609</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6556</v>
+        <v>3.7656</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7813</v>
+        <v>0.5589</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8743</v>
+        <v>3.2067</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7824</v>
+        <v>1.429</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2483</v>
+        <v>1.1748</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5341</v>
+        <v>0.2542</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5091</v>
+        <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2109</v>
+        <v>0.3573</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2683</v>
+        <v>-0.0013</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0575</v>
+        <v>0.3586</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.6127</v>
+        <v>5.9908</v>
       </c>
       <c r="E16" t="n">
-        <v>3.511</v>
+        <v>3.2106</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1017</v>
+        <v>2.7801</v>
       </c>
       <c r="G16" t="n">
         <v>4.3158</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5249</v>
+        <v>0.9029</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2208</v>
+        <v>-0.0796</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3041</v>
+        <v>0.9825</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ARIZTIMUÑO MORRAS</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4551</v>
+        <v>4.1388</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6665</v>
+        <v>1.7548</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7886</v>
+        <v>2.384</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3901</v>
+        <v>3.0102</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3719</v>
+        <v>2.8017</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9818</v>
+        <v>0.2085</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8777</v>
+        <v>1.9753</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2186</v>
+        <v>2.5615</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6591</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4875</v>
+        <v>1.0349</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1533</v>
+        <v>0.2402</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6408</v>
+        <v>0.7947</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1231</v>
+        <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0602</v>
+        <v>0.4495</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6214</v>
+        <v>-0.2204</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4389</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>2.7418</v>
+        <v>-0.2859</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0277</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.2859</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>M. ARIZTIMUÑO MORRAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7045</v>
+        <v>3.6735</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4544</v>
+        <v>2.9655</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2501</v>
+        <v>0.7079</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0102</v>
+        <v>2.3901</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8017</v>
+        <v>3.3719</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2085</v>
+        <v>-0.9818</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9753</v>
+        <v>3.8777</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5615</v>
+        <v>3.2186</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.6591</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0349</v>
+        <v>-1.4875</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2402</v>
+        <v>0.1533</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7947</v>
+        <v>-1.6408</v>
       </c>
       <c r="P18" t="n">
-        <v>0.965</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R18" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0152</v>
+        <v>0.2786</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5208</v>
+        <v>-0.0796</v>
       </c>
       <c r="U18" t="n">
-        <v>0.536</v>
+        <v>0.3582</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2859</v>
+        <v>2.7418</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.0277</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2859</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6399</v>
+        <v>3.0137</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1236</v>
+        <v>-0.7231</v>
       </c>
       <c r="F19" t="n">
-        <v>3.7636</v>
+        <v>3.7368</v>
       </c>
       <c r="G19" t="n">
         <v>1.0368</v>
@@ -1936,13 +1936,13 @@
         <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>0.117</v>
+        <v>0.4908</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5208</v>
+        <v>-0.1203</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6378</v>
+        <v>0.6111</v>
       </c>
       <c r="V19" t="n">
         <v>0.3281</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1535</v>
+        <v>1.0659</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4565</v>
+        <v>1.5567</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3031</v>
+        <v>-0.4908</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2227</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1679</v>
+        <v>-0.2555</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4759</v>
+        <v>-0.3758</v>
       </c>
       <c r="U20" t="n">
-        <v>0.308</v>
+        <v>0.1203</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2808</v>
+        <v>0.3277</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5112</v>
+        <v>-1.8116</v>
       </c>
       <c r="F21" t="n">
-        <v>1.792</v>
+        <v>2.1393</v>
       </c>
       <c r="G21" t="n">
         <v>2.124</v>
@@ -2092,13 +2092,13 @@
         <v>2.7021</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0059</v>
+        <v>0.041</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2697</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2637</v>
+        <v>0.6111</v>
       </c>
       <c r="V21" t="n">
         <v>0.2859</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3576</v>
+        <v>-0.3041</v>
       </c>
       <c r="E22" t="n">
         <v>-0.7659</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4083</v>
+        <v>0.4618</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6603</v>
@@ -2170,13 +2170,13 @@
         <v>0.386</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0833</v>
+        <v>-0.0297</v>
       </c>
       <c r="T22" t="n">
         <v>-0.119</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2045</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7157</v>
+        <v>-1.6155</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5112</v>
+        <v>1.0727</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9844000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>1.7371</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9921</v>
+        <v>-0.3305</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6398</v>
+        <v>-0.5397</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3523</v>
+        <v>0.2092</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1454</v>
+        <v>-2.0449</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8044</v>
+        <v>-2.1048</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3409</v>
+        <v>0.06</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2491</v>
@@ -2326,13 +2326,13 @@
         <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0892</v>
+        <v>0.0112</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0912</v>
+        <v>-0.3916</v>
       </c>
       <c r="U24" t="n">
-        <v>0.002</v>
+        <v>0.4028</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>32.1815</v>
+        <v>33.5168</v>
       </c>
       <c r="E25" t="n">
-        <v>11.1815</v>
+        <v>11.1816</v>
       </c>
       <c r="F25" t="n">
-        <v>21.0001</v>
+        <v>22.3352</v>
       </c>
       <c r="G25" t="n">
         <v>20.393</v>
@@ -2374,7 +2374,7 @@
         <v>18.2938</v>
       </c>
       <c r="I25" t="n">
-        <v>2.099300000000002</v>
+        <v>2.0993</v>
       </c>
       <c r="J25" t="n">
         <v>21.388</v>
@@ -2386,13 +2386,13 @@
         <v>7.665199999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9949999999999993</v>
+        <v>-0.9949999999999989</v>
       </c>
       <c r="N25" t="n">
         <v>4.5708</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.5658</v>
+        <v>-5.565799999999999</v>
       </c>
       <c r="P25" t="n">
         <v>5.7901</v>
@@ -2404,13 +2404,13 @@
         <v>19.3008</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0444</v>
+        <v>2.3796</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.4652</v>
+        <v>-2.4653</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5097</v>
+        <v>4.844799999999999</v>
       </c>
       <c r="V25" t="n">
         <v>4.9541</v>
